--- a/lab-standards/BACCO-lab-standard.xlsx
+++ b/lab-standards/BACCO-lab-standard.xlsx
@@ -560,6 +560,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -572,6 +576,10 @@
           <t>Classroom cum workshop – 500 sft (46 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -641,7 +649,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -663,7 +673,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>6</v>
       </c>
@@ -685,7 +697,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>6</v>
       </c>
@@ -708,7 +722,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -731,7 +747,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -753,7 +771,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -775,7 +795,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -797,7 +819,9 @@
       <c r="C23" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -819,7 +843,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -841,7 +867,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -863,7 +891,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -885,7 +915,9 @@
       <c r="C27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -907,7 +939,9 @@
       <c r="C28" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -929,7 +963,9 @@
       <c r="C29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -1075,6 +1111,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1087,6 +1127,10 @@
           <t>Classroom cum workshop – 500 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1156,7 +1200,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -1178,7 +1224,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>6</v>
       </c>
@@ -1200,7 +1248,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>6</v>
       </c>
@@ -1223,7 +1273,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -1246,7 +1298,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -1268,7 +1322,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -1290,7 +1346,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -1312,7 +1370,9 @@
       <c r="C23" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -1334,7 +1394,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -1356,7 +1418,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -1378,7 +1442,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -1400,7 +1466,9 @@
       <c r="C27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -1422,7 +1490,9 @@
       <c r="C28" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -1444,7 +1514,9 @@
       <c r="C29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -1590,6 +1662,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1602,6 +1678,10 @@
           <t>Classroom cum workshop – 500 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1671,7 +1751,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -1693,7 +1775,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>6</v>
       </c>
@@ -1715,7 +1799,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>6</v>
       </c>
@@ -1738,7 +1824,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -1761,7 +1849,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -1783,7 +1873,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -1805,7 +1897,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -1827,7 +1921,9 @@
       <c r="C23" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -1849,7 +1945,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -1871,7 +1969,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -1893,7 +1993,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -1915,7 +2017,9 @@
       <c r="C27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -1937,7 +2041,9 @@
       <c r="C28" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -1959,7 +2065,9 @@
       <c r="C29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -2105,6 +2213,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2117,6 +2229,10 @@
           <t>Classroom cum workshop – 500 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2186,7 +2302,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -2208,7 +2326,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>6</v>
       </c>
@@ -2230,7 +2350,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>6</v>
       </c>
@@ -2253,7 +2375,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -2276,7 +2400,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -2298,7 +2424,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -2320,7 +2448,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -2342,7 +2472,9 @@
       <c r="C23" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -2364,7 +2496,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -2386,7 +2520,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -2408,7 +2544,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -2430,7 +2568,9 @@
       <c r="C27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -2452,7 +2592,9 @@
       <c r="C28" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -2474,7 +2616,9 @@
       <c r="C29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -2620,6 +2764,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2632,6 +2780,10 @@
           <t>Classroom cum workshop – 500 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2701,7 +2853,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -2723,7 +2877,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>6</v>
       </c>
@@ -2745,7 +2901,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>6</v>
       </c>
@@ -2768,7 +2926,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -2791,7 +2951,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -2813,7 +2975,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -2835,7 +2999,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -2857,7 +3023,9 @@
       <c r="C23" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -2879,7 +3047,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -2901,7 +3071,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -2923,7 +3095,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -2945,7 +3119,9 @@
       <c r="C27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -2967,7 +3143,9 @@
       <c r="C28" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -2989,7 +3167,9 @@
       <c r="C29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
